--- a/docs/alliance-templates/alliance-permissions.xlsx
+++ b/docs/alliance-templates/alliance-permissions.xlsx
@@ -7,38 +7,56 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="合作权限" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作权限'!$A$2:$C$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>填写说明：
-* 必填列。
-账号类型：enterprise（企业） / expert（专家），默认为 enterprise
-是否启用：true / false 或 是 / 否，默认为 true（启用）</t>
-  </si>
-  <si>
-    <t>账号名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>账号名称</t>
   </si>
   <si>
     <t>账号类型</t>
   </si>
   <si>
     <t>是否启用</t>
+  </si>
+  <si>
+    <t>华为企业账号</t>
+  </si>
+  <si>
+    <t>enterprise</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>阿里企业账号</t>
+  </si>
+  <si>
+    <t>刘建国专家账号</t>
+  </si>
+  <si>
+    <t>expert</t>
+  </si>
+  <si>
+    <t>比亚迪企业账号</t>
+  </si>
+  <si>
+    <t>孙晓华专家账号</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,14 +66,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,34 +91,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -373,38 +369,84 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="3" min="3" width="14"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="16"/>
+    <col customWidth="true" max="3" min="3" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="80" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$C$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$C$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-permissions.xlsx
+++ b/docs/alliance-templates/alliance-permissions.xlsx
@@ -1,62 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作权限" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'合作权限'!$A$2:$C$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>账号名称</t>
-  </si>
-  <si>
-    <t>账号类型</t>
-  </si>
-  <si>
-    <t>是否启用</t>
-  </si>
-  <si>
-    <t>华为企业账号</t>
-  </si>
-  <si>
-    <t>enterprise</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>阿里企业账号</t>
-  </si>
-  <si>
-    <t>刘建国专家账号</t>
-  </si>
-  <si>
-    <t>expert</t>
-  </si>
-  <si>
-    <t>比亚迪企业账号</t>
-  </si>
-  <si>
-    <t>孙晓华专家账号</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -370,83 +443,138 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="22"/>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="3" min="3" width="12"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
+    <row r="1" ht="96" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+账号类型：enterprise（企业） / expert（专家），默认为 enterprise
+是否启用：true / false 或 是 / 否，默认为 true（启用）</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>账号名称 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>账号类型</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>华为企业账号</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>阿里企业账号</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>刘建国专家账号</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>比亚迪企业账号</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>孙晓华专家账号</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$C$6"/>
+  <autoFilter ref="A2:C2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-permissions.xlsx
+++ b/docs/alliance-templates/alliance-permissions.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作权限" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,8 +511,8 @@
 是否启用：true / false 或 是 / 否，默认为 true（启用）</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -493,12 +539,12 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>enterprise</t>
+          <t>企业账号</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -510,12 +556,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>enterprise</t>
+          <t>企业账号</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -527,12 +573,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>专家账号</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -544,12 +590,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>enterprise</t>
+          <t>企业账号</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -561,12 +607,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>专家账号</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
     </row>
